--- a/XLibur.Tests/Resource/Examples/Columns/ColumnCollection.xlsx
+++ b/XLibur.Tests/Resource/Examples/Columns/ColumnCollection.xlsx
@@ -445,13 +445,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:V6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="22" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="22" width="3.710625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:22">
@@ -514,43 +511,32 @@
       <x:c r="V6" s="7"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="2" width="3.710625" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="3.710625" customWidth="1"/>
     <x:col min="4" max="5" width="3.710625" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="3.710625" customWidth="1"/>
     <x:col min="7" max="8" width="3.710625" style="4" customWidth="1"/>
-    <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="3.710625" customWidth="1"/>
     <x:col min="10" max="11" width="3.710625" style="5" customWidth="1"/>
-    <x:col min="12" max="12" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="3.710625" customWidth="1"/>
     <x:col min="13" max="14" width="3.710625" style="5" customWidth="1"/>
-    <x:col min="15" max="15" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="3.710625" customWidth="1"/>
     <x:col min="16" max="17" width="3.710625" style="6" customWidth="1"/>
-    <x:col min="18" max="18" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="18" max="18" width="3.710625" customWidth="1"/>
     <x:col min="19" max="20" width="3.710625" style="6" customWidth="1"/>
-    <x:col min="21" max="21" width="3.710625" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="3.710625" customWidth="1"/>
     <x:col min="22" max="22" width="3.710625" style="7" customWidth="1"/>
   </x:cols>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Columns/ColumnCollection.xlsx
+++ b/XLibur.Tests/Resource/Examples/Columns/ColumnCollection.xlsx
@@ -448,7 +448,7 @@
   <x:dimension ref="A1:V6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="22" width="3.710625" customWidth="1"/>
+    <x:col min="1" max="22" width="3.714286" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:22">
@@ -520,21 +520,21 @@
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="2" width="3.710625" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="3.710625" customWidth="1"/>
-    <x:col min="4" max="5" width="3.710625" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="3.710625" customWidth="1"/>
-    <x:col min="7" max="8" width="3.710625" style="4" customWidth="1"/>
-    <x:col min="9" max="9" width="3.710625" customWidth="1"/>
-    <x:col min="10" max="11" width="3.710625" style="5" customWidth="1"/>
-    <x:col min="12" max="12" width="3.710625" customWidth="1"/>
-    <x:col min="13" max="14" width="3.710625" style="5" customWidth="1"/>
-    <x:col min="15" max="15" width="3.710625" customWidth="1"/>
-    <x:col min="16" max="17" width="3.710625" style="6" customWidth="1"/>
-    <x:col min="18" max="18" width="3.710625" customWidth="1"/>
-    <x:col min="19" max="20" width="3.710625" style="6" customWidth="1"/>
-    <x:col min="21" max="21" width="3.710625" customWidth="1"/>
-    <x:col min="22" max="22" width="3.710625" style="7" customWidth="1"/>
+    <x:col min="1" max="2" width="3.714286" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="3.714286" customWidth="1"/>
+    <x:col min="4" max="5" width="3.714286" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="3.714286" customWidth="1"/>
+    <x:col min="7" max="8" width="3.714286" style="4" customWidth="1"/>
+    <x:col min="9" max="9" width="3.714286" customWidth="1"/>
+    <x:col min="10" max="11" width="3.714286" style="5" customWidth="1"/>
+    <x:col min="12" max="12" width="3.714286" customWidth="1"/>
+    <x:col min="13" max="14" width="3.714286" style="5" customWidth="1"/>
+    <x:col min="15" max="15" width="3.714286" customWidth="1"/>
+    <x:col min="16" max="17" width="3.714286" style="6" customWidth="1"/>
+    <x:col min="18" max="18" width="3.714286" customWidth="1"/>
+    <x:col min="19" max="20" width="3.714286" style="6" customWidth="1"/>
+    <x:col min="21" max="21" width="3.714286" customWidth="1"/>
+    <x:col min="22" max="22" width="3.714286" style="7" customWidth="1"/>
   </x:cols>
   <x:sheetData/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
